--- a/artfynd/A 18744-2024 artfynd.xlsx
+++ b/artfynd/A 18744-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117703562</v>
+        <v>117703560</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>74531</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sö. Tappebosjön, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575057</v>
+        <v>575062</v>
       </c>
       <c r="R2" t="n">
-        <v>6649537</v>
+        <v>6649536</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117703560</v>
+        <v>117703559</v>
       </c>
       <c r="B3" t="n">
-        <v>74531</v>
+        <v>96791</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sö. Tappebosjön, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575062</v>
+        <v>574948</v>
       </c>
       <c r="R3" t="n">
-        <v>6649536</v>
+        <v>6649464</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -864,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117703559</v>
+        <v>117703562</v>
       </c>
       <c r="B4" t="n">
-        <v>96791</v>
+        <v>97836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574948</v>
+        <v>575057</v>
       </c>
       <c r="R4" t="n">
-        <v>6649464</v>
+        <v>6649537</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 18744-2024 artfynd.xlsx
+++ b/artfynd/A 18744-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117703560</v>
+        <v>117703559</v>
       </c>
       <c r="B2" t="n">
-        <v>74531</v>
+        <v>96793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sö. Tappebosjön, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575062</v>
+        <v>574948</v>
       </c>
       <c r="R2" t="n">
-        <v>6649536</v>
+        <v>6649464</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -762,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117703559</v>
+        <v>117703562</v>
       </c>
       <c r="B3" t="n">
-        <v>96791</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574948</v>
+        <v>575057</v>
       </c>
       <c r="R3" t="n">
-        <v>6649464</v>
+        <v>6649537</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117703562</v>
+        <v>117703560</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>74533</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sö. Tappebosjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575057</v>
+        <v>575062</v>
       </c>
       <c r="R4" t="n">
-        <v>6649537</v>
+        <v>6649536</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -967,6 +966,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
